--- a/data/awards.xlsx
+++ b/data/awards.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/max/Library/CloudStorage/GoogleDrive-rmaxsmth@gmail.com/My Drive/FF/TRUFFLE/TRUFFLEdashGIT/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/maxsmith/Library/CloudStorage/GoogleDrive-rmaxsmth@gmail.com/My Drive/FF/TRUFFLE/TRUFFLEdashGIT/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6AF0C23-6441-BE4F-920A-A5FC3D7620D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C2CEF7-07F8-304B-918C-87CD6DEF0B13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="16440" xr2:uid="{C9430D62-D1F7-BB47-A467-F7279DABC2AE}"/>
   </bookViews>
   <sheets>
     <sheet name="awards" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="285">
   <si>
     <t>League</t>
   </si>
@@ -818,6 +831,63 @@
   </si>
   <si>
     <t>11-2</t>
+  </si>
+  <si>
+    <t>www/graphics/teamlogos/AFL.png</t>
+  </si>
+  <si>
+    <t>Arctic Fighting Lemurloos</t>
+  </si>
+  <si>
+    <t>www/graphics/execs/barrett.png</t>
+  </si>
+  <si>
+    <t>Barrett Gess</t>
+  </si>
+  <si>
+    <t>Jayden Daniels</t>
+  </si>
+  <si>
+    <t>www/graphics/players/jdaniels.png</t>
+  </si>
+  <si>
+    <t>Bijan Robinson</t>
+  </si>
+  <si>
+    <t>www/graphics/players/brobinson.png</t>
+  </si>
+  <si>
+    <t>Christian McCaffrey ($145)</t>
+  </si>
+  <si>
+    <t>Jonnu Smith ($12)</t>
+  </si>
+  <si>
+    <t>www/graphics/players/jsmith.png</t>
+  </si>
+  <si>
+    <t>Chuba Hubbard ($3)</t>
+  </si>
+  <si>
+    <t>www/graphics/players/chubbard.png</t>
+  </si>
+  <si>
+    <t>Brock Bowers</t>
+  </si>
+  <si>
+    <t>Jahmyr Gibbs</t>
+  </si>
+  <si>
+    <t>Joe Burrow</t>
+  </si>
+  <si>
+    <t>Brian Thomas</t>
+  </si>
+  <si>
+    <t>Terry McLaurin</t>
+  </si>
+  <si>
+    <t>James Cook</t>
   </si>
 </sst>
 </file>
@@ -1686,9 +1756,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2105072D-50C6-D441-A50A-97C78FFD136E}">
-  <dimension ref="A1:H262"/>
+  <dimension ref="A1:H291"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="4" max="4" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -7532,6 +7605,652 @@
         <v>74</v>
       </c>
     </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A263" t="s">
+        <v>7</v>
+      </c>
+      <c r="B263" t="s">
+        <v>8</v>
+      </c>
+      <c r="C263">
+        <v>2024</v>
+      </c>
+      <c r="D263" t="s">
+        <v>9</v>
+      </c>
+      <c r="E263" t="s">
+        <v>266</v>
+      </c>
+      <c r="F263" t="s">
+        <v>267</v>
+      </c>
+      <c r="G263" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H263" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A264" t="s">
+        <v>7</v>
+      </c>
+      <c r="B264" t="s">
+        <v>13</v>
+      </c>
+      <c r="C264">
+        <v>2024</v>
+      </c>
+      <c r="D264" t="s">
+        <v>14</v>
+      </c>
+      <c r="E264" t="s">
+        <v>87</v>
+      </c>
+      <c r="F264" t="s">
+        <v>88</v>
+      </c>
+      <c r="G264" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H264" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A265" t="s">
+        <v>7</v>
+      </c>
+      <c r="B265" t="s">
+        <v>18</v>
+      </c>
+      <c r="C265">
+        <v>2024</v>
+      </c>
+      <c r="D265" t="s">
+        <v>19</v>
+      </c>
+      <c r="E265" t="s">
+        <v>20</v>
+      </c>
+      <c r="F265" t="s">
+        <v>148</v>
+      </c>
+      <c r="G265" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="H265" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A266" t="s">
+        <v>7</v>
+      </c>
+      <c r="B266" t="s">
+        <v>23</v>
+      </c>
+      <c r="C266">
+        <v>2024</v>
+      </c>
+      <c r="D266" t="s">
+        <v>24</v>
+      </c>
+      <c r="E266" t="s">
+        <v>268</v>
+      </c>
+      <c r="F266" t="s">
+        <v>269</v>
+      </c>
+      <c r="G266" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H266" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>7</v>
+      </c>
+      <c r="B267" t="s">
+        <v>28</v>
+      </c>
+      <c r="C267">
+        <v>2024</v>
+      </c>
+      <c r="D267" t="s">
+        <v>29</v>
+      </c>
+      <c r="E267" t="s">
+        <v>42</v>
+      </c>
+      <c r="F267" t="s">
+        <v>43</v>
+      </c>
+      <c r="G267" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H267" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A268" t="s">
+        <v>7</v>
+      </c>
+      <c r="B268" t="s">
+        <v>34</v>
+      </c>
+      <c r="C268">
+        <v>2024</v>
+      </c>
+      <c r="D268" t="s">
+        <v>35</v>
+      </c>
+      <c r="E268" t="s">
+        <v>271</v>
+      </c>
+      <c r="F268" t="s">
+        <v>270</v>
+      </c>
+      <c r="G268" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H268" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A269" t="s">
+        <v>7</v>
+      </c>
+      <c r="B269" t="s">
+        <v>40</v>
+      </c>
+      <c r="C269">
+        <v>2024</v>
+      </c>
+      <c r="D269" t="s">
+        <v>41</v>
+      </c>
+      <c r="E269" t="s">
+        <v>271</v>
+      </c>
+      <c r="F269" t="s">
+        <v>270</v>
+      </c>
+      <c r="G269" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H269" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A270" t="s">
+        <v>7</v>
+      </c>
+      <c r="B270" t="s">
+        <v>45</v>
+      </c>
+      <c r="C270">
+        <v>2024</v>
+      </c>
+      <c r="D270" t="s">
+        <v>46</v>
+      </c>
+      <c r="E270" t="s">
+        <v>273</v>
+      </c>
+      <c r="F270" t="s">
+        <v>272</v>
+      </c>
+      <c r="G270" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H270" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A271" t="s">
+        <v>7</v>
+      </c>
+      <c r="B271" t="s">
+        <v>49</v>
+      </c>
+      <c r="C271">
+        <v>2024</v>
+      </c>
+      <c r="D271" t="s">
+        <v>50</v>
+      </c>
+      <c r="E271" t="s">
+        <v>30</v>
+      </c>
+      <c r="F271" t="s">
+        <v>274</v>
+      </c>
+      <c r="G271" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H271" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>7</v>
+      </c>
+      <c r="B272" t="s">
+        <v>54</v>
+      </c>
+      <c r="C272">
+        <v>2024</v>
+      </c>
+      <c r="D272" t="s">
+        <v>55</v>
+      </c>
+      <c r="E272" t="s">
+        <v>276</v>
+      </c>
+      <c r="F272" t="s">
+        <v>275</v>
+      </c>
+      <c r="G272" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H272" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>7</v>
+      </c>
+      <c r="B273" t="s">
+        <v>58</v>
+      </c>
+      <c r="C273">
+        <v>2024</v>
+      </c>
+      <c r="D273" t="s">
+        <v>59</v>
+      </c>
+      <c r="E273" t="s">
+        <v>278</v>
+      </c>
+      <c r="F273" t="s">
+        <v>277</v>
+      </c>
+      <c r="G273" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H273" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>7</v>
+      </c>
+      <c r="C274">
+        <v>2024</v>
+      </c>
+      <c r="D274" t="s">
+        <v>61</v>
+      </c>
+      <c r="F274" t="s">
+        <v>43</v>
+      </c>
+      <c r="G274" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H274" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>7</v>
+      </c>
+      <c r="C275">
+        <v>2024</v>
+      </c>
+      <c r="D275" t="s">
+        <v>61</v>
+      </c>
+      <c r="F275" t="s">
+        <v>201</v>
+      </c>
+      <c r="G275" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H275" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>7</v>
+      </c>
+      <c r="C276">
+        <v>2024</v>
+      </c>
+      <c r="D276" t="s">
+        <v>61</v>
+      </c>
+      <c r="F276" t="s">
+        <v>76</v>
+      </c>
+      <c r="G276" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H276" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>7</v>
+      </c>
+      <c r="C277">
+        <v>2024</v>
+      </c>
+      <c r="D277" t="s">
+        <v>61</v>
+      </c>
+      <c r="F277" t="s">
+        <v>121</v>
+      </c>
+      <c r="G277" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H277" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>7</v>
+      </c>
+      <c r="C278">
+        <v>2024</v>
+      </c>
+      <c r="D278" t="s">
+        <v>61</v>
+      </c>
+      <c r="F278" t="s">
+        <v>139</v>
+      </c>
+      <c r="G278" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H278" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
+        <v>7</v>
+      </c>
+      <c r="C279">
+        <v>2024</v>
+      </c>
+      <c r="D279" t="s">
+        <v>61</v>
+      </c>
+      <c r="F279" t="s">
+        <v>279</v>
+      </c>
+      <c r="G279" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H279" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>7</v>
+      </c>
+      <c r="C280">
+        <v>2024</v>
+      </c>
+      <c r="D280" t="s">
+        <v>61</v>
+      </c>
+      <c r="F280" t="s">
+        <v>280</v>
+      </c>
+      <c r="G280" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H280" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>7</v>
+      </c>
+      <c r="C281">
+        <v>2024</v>
+      </c>
+      <c r="D281" t="s">
+        <v>61</v>
+      </c>
+      <c r="F281" t="s">
+        <v>67</v>
+      </c>
+      <c r="G281" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H281" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>7</v>
+      </c>
+      <c r="C282">
+        <v>2024</v>
+      </c>
+      <c r="D282" t="s">
+        <v>61</v>
+      </c>
+      <c r="F282" t="s">
+        <v>62</v>
+      </c>
+      <c r="G282" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H282" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
+        <v>7</v>
+      </c>
+      <c r="C283">
+        <v>2024</v>
+      </c>
+      <c r="D283" t="s">
+        <v>72</v>
+      </c>
+      <c r="F283" t="s">
+        <v>270</v>
+      </c>
+      <c r="G283" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H283" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A284" t="s">
+        <v>7</v>
+      </c>
+      <c r="C284">
+        <v>2024</v>
+      </c>
+      <c r="D284" t="s">
+        <v>72</v>
+      </c>
+      <c r="F284" t="s">
+        <v>179</v>
+      </c>
+      <c r="G284" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H284" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A285" t="s">
+        <v>7</v>
+      </c>
+      <c r="C285">
+        <v>2024</v>
+      </c>
+      <c r="D285" t="s">
+        <v>72</v>
+      </c>
+      <c r="F285" t="s">
+        <v>272</v>
+      </c>
+      <c r="G285" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H285" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A286" t="s">
+        <v>7</v>
+      </c>
+      <c r="C286">
+        <v>2024</v>
+      </c>
+      <c r="D286" t="s">
+        <v>72</v>
+      </c>
+      <c r="F286" t="s">
+        <v>282</v>
+      </c>
+      <c r="G286" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H286" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A287" t="s">
+        <v>7</v>
+      </c>
+      <c r="C287">
+        <v>2024</v>
+      </c>
+      <c r="D287" t="s">
+        <v>72</v>
+      </c>
+      <c r="F287" t="s">
+        <v>283</v>
+      </c>
+      <c r="G287" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H287" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A288" t="s">
+        <v>7</v>
+      </c>
+      <c r="C288">
+        <v>2024</v>
+      </c>
+      <c r="D288" t="s">
+        <v>72</v>
+      </c>
+      <c r="F288" t="s">
+        <v>113</v>
+      </c>
+      <c r="G288" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H288" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A289" t="s">
+        <v>7</v>
+      </c>
+      <c r="C289">
+        <v>2024</v>
+      </c>
+      <c r="D289" t="s">
+        <v>72</v>
+      </c>
+      <c r="F289" t="s">
+        <v>64</v>
+      </c>
+      <c r="G289" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H289" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>7</v>
+      </c>
+      <c r="C290">
+        <v>2024</v>
+      </c>
+      <c r="D290" t="s">
+        <v>72</v>
+      </c>
+      <c r="F290" t="s">
+        <v>284</v>
+      </c>
+      <c r="G290" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H290" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A291" t="s">
+        <v>7</v>
+      </c>
+      <c r="C291">
+        <v>2024</v>
+      </c>
+      <c r="D291" t="s">
+        <v>72</v>
+      </c>
+      <c r="F291" t="s">
+        <v>281</v>
+      </c>
+      <c r="G291" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H291" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
